--- a/docs/audit-final/CAXE-inventaire-questions.xlsx
+++ b/docs/audit-final/CAXE-inventaire-questions.xlsx
@@ -1391,7 +1391,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>reformulée : « Part de vos ventes » ambigu (nombre de commandes ou chiffre d'affaires ?) et sans période ; l'aide parle de commandes. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>reformulée : « Part de vos ventes » ambigu (nombre de commandes ou chiffre d'affaires ?) et sans période ; l'aide parle de commandes. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (canaux, rapides) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, canaux, rapides) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-10 | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-10 | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>conforme : « Vos 3 principaux partenaires » : le tableau accepte 3 lignes au plus, le texte est cohérent. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>conforme : « Vos 3 principaux partenaires » : le tableau accepte 3 lignes au plus, le texte est cohérent. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en % | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en % | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (partages) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, partages) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (partages) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, partages) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (partages) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, partages) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (partages) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | A-02 corrigée le 29 octobre (Navigateur : P-07a à P-07d, P-13 à P-19b conformes (dont la reprise non enregistrée, la question complétée puis enregistrée, la modification depuis l'autre agent et après actualisation))</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, partages) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | A-02 corrigée le 29 octobre (Navigateur : P-07a à P-07d, P-13 à P-19b conformes (dont la reprise non enregistrée, la question complétée puis enregistrée, la modification depuis l'autre agent et après actualisation))</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>reformulée : Période absente pour une part de chiffre d'affaires. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
+          <t>reformulée : Période absente pour une part de chiffre d'affaires. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : comparée dans data/evolutions.json</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : comparée dans data/evolutions.json</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (resultats, rapides, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), resultats, rapides, boutons de réponse)</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (resultats, rapides, boutons de réponse) | contrôle automatique : relance : condition à vérifier → conforme : posée si le problème existe (appels manqués, devis, relances)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, resultats, rapides, boutons de réponse) | contrôle automatique : relance : condition à vérifier → conforme : posée si le problème existe (appels manqués, devis, relances)</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : relance : condition à vérifier → pratique sans problème constaté (A-17)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : relance : condition à vérifier → pratique sans problème constaté (A-17)</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : relance : condition à vérifier → conforme : posée si le problème existe (appels manqués, devis, relances)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, règles d'affichage (réponse changée à l'écran)) | contrôle automatique : relance : condition à vérifier → conforme : posée si le problème existe (appels manqués, devis, relances)</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : relance : condition à vérifier → conforme : posée si le problème existe (appels manqués, devis, relances)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : relance : condition à vérifier → conforme : posée si le problème existe (appels manqués, devis, relances)</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : relance : condition à vérifier → conforme : posée si le problème existe (appels manqués, devis, relances)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : relance : condition à vérifier → conforme : posée si le problème existe (appels manqués, devis, relances)</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : relance : condition à vérifier → conforme : posée si le problème existe (appels manqués, devis, relances)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : relance : condition à vérifier → conforme : posée si le problème existe (appels manqués, devis, relances)</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>reformulée : Période absente pour une part de chiffre d'affaires. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
+          <t>reformulée : Période absente pour une part de chiffre d'affaires. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : canal ou outil : condition à vérifier → conforme : profil e-commerce ; pratique à relier aux paniers abandonnés (A-17) | contrôle automatique : relance : condition à vérifier → pratique sans problème constaté (A-17)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : canal ou outil : condition à vérifier → conforme : profil e-commerce ; pratique à relier aux paniers abandonnés (A-17) | contrôle automatique : relance : condition à vérifier → pratique sans problème constaté (A-17)</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>reformulée : Période absente pour une part de chiffre d'affaires. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
+          <t>reformulée : Période absente pour une part de chiffre d'affaires. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : comparée dans data/evolutions.json</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : comparée dans data/evolutions.json</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json)</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-10 | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json) | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-10 | contrôle automatique : texte très proche d'une autre question → conforme : même donnée, posée une seule fois (jumelle ou correspondance, data/partages.json) | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
         </is>
       </c>
       <c r="O146" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>à arbitrer : Le texte demande les créneaux proposés par semaine ; l'aide (« Les créneaux réservés sont déjà comptés avec vos rendez-vous ») laisse entendre qu'il ne faut compter que les créneaux libres. Les deux donnent des chiffres différents : laquelle des deux mesures le calcul de capacité attend-il ? Rien n'est modifié en attendant. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>à arbitrer : Le texte demande les créneaux proposés par semaine ; l'aide (« Les créneaux réservés sont déjà comptés avec vos rendez-vous ») laisse entendre qu'il ne faut compter que les créneaux libres. Les deux donnent des chiffres différents : laquelle des deux mesures le calcul de capacité attend-il ? Rien n'est modifié en attendant. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-10</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-10</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O172" s="2" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="N183" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O183" s="2" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O186" s="2" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="N187" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O187" s="2" t="inlineStr">
@@ -16671,7 +16671,7 @@
       </c>
       <c r="N188" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : fait daté ou tendance déclarée, pas une évolution calculée</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : fait daté ou tendance déclarée, pas une évolution calculée</t>
         </is>
       </c>
       <c r="O188" s="2" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="N189" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O189" s="2" t="inlineStr">
@@ -16839,7 +16839,7 @@
       </c>
       <c r="N190" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O190" s="2" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="N191" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O191" s="2" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | A-02 corrigée le 29 octobre (Navigateur : P-07a à P-07d, P-13 à P-19b conformes (dont la reprise non enregistrée, la question complétée puis enregistrée, la modification depuis l'autre agent et après actualisation))</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | A-02 corrigée le 29 octobre (Navigateur : P-07a à P-07d, P-13 à P-19b conformes (dont la reprise non enregistrée, la question complétée puis enregistrée, la modification depuis l'autre agent et après actualisation))</t>
         </is>
       </c>
       <c r="O196" s="2" t="inlineStr">
@@ -17447,7 +17447,7 @@
       </c>
       <c r="N197" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O197" s="2" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | A-02 corrigée le 29 octobre (Navigateur : P-07a à P-07d, P-13 à P-19b conformes (dont la reprise non enregistrée, la question complétée puis enregistrée, la modification depuis l'autre agent et après actualisation))</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | A-02 corrigée le 29 octobre (Navigateur : P-07a à P-07d, P-13 à P-19b conformes (dont la reprise non enregistrée, la question complétée puis enregistrée, la modification depuis l'autre agent et après actualisation))</t>
         </is>
       </c>
       <c r="O198" s="2" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O199" s="2" t="inlineStr">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : fait daté ou tendance déclarée, pas une évolution calculée</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : fait daté ou tendance déclarée, pas une évolution calculée</t>
         </is>
       </c>
       <c r="O200" s="2" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="N210" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O210" s="2" t="inlineStr">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="N211" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O211" s="2" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O212" s="2" t="inlineStr">
@@ -18827,7 +18827,7 @@
       </c>
       <c r="N213" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O213" s="2" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="N214" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O214" s="2" t="inlineStr">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="N215" s="2" t="inlineStr">
         <is>
-          <t>à arbitrer : Répartition « des paiements » : on ne sait pas s'il faut compter les paiements (nombre de factures) ou les montants, et sans période. Pour la trésorerie, c'est le montant qui compte (interprétation). Période ajoutée ; la mesure (nombre ou montant) reste à trancher. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>à arbitrer : Répartition « des paiements » : on ne sait pas s'il faut compter les paiements (nombre de factures) ou les montants, et sans période. Pour la trésorerie, c'est le montant qui compte (interprétation). Période ajoutée ; la mesure (nombre ou montant) reste à trancher. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O215" s="2" t="inlineStr">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="N216" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles</t>
         </is>
       </c>
       <c r="O216" s="2" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="N217" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : fait daté ou tendance déclarée, pas une évolution calculée</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : fait daté ou tendance déclarée, pas une évolution calculée</t>
         </is>
       </c>
       <c r="O217" s="2" t="inlineStr">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="N218" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O218" s="2" t="inlineStr">
@@ -19343,7 +19343,7 @@
       </c>
       <c r="N219" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O219" s="2" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="N220" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O220" s="2" t="inlineStr">
@@ -19511,7 +19511,7 @@
       </c>
       <c r="N221" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O221" s="2" t="inlineStr">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="N222" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : relance : condition à vérifier → pratique sans problème constaté (A-17)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : relance : condition à vérifier → pratique sans problème constaté (A-17)</t>
         </is>
       </c>
       <c r="O222" s="2" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="N223" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O223" s="2" t="inlineStr">
@@ -19779,7 +19779,7 @@
       </c>
       <c r="N224" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O224" s="2" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="N225" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles</t>
         </is>
       </c>
       <c r="O225" s="2" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="N226" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O226" s="2" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="N227" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O227" s="2" t="inlineStr">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="N228" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O228" s="2" t="inlineStr">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="N229" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O229" s="2" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="N230" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O230" s="2" t="inlineStr">
@@ -20375,7 +20375,7 @@
       </c>
       <c r="N231" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O231" s="2" t="inlineStr">
@@ -20459,7 +20459,7 @@
       </c>
       <c r="N232" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O232" s="2" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="N233" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O233" s="2" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="N234" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11)</t>
         </is>
       </c>
       <c r="O234" s="2" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="N235" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11)</t>
         </is>
       </c>
       <c r="O235" s="2" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="N236" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O236" s="2" t="inlineStr">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="N237" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O237" s="2" t="inlineStr">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="N238" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O238" s="2" t="inlineStr">
@@ -21063,7 +21063,7 @@
       </c>
       <c r="N239" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : financement : condition à vérifier → conforme : posée si crédit (D10) ou découvert (D11)</t>
         </is>
       </c>
       <c r="O239" s="2" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="N240" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O240" s="2" t="inlineStr">
@@ -21231,7 +21231,7 @@
       </c>
       <c r="N241" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O241" s="2" t="inlineStr">
@@ -21315,7 +21315,7 @@
       </c>
       <c r="N242" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O242" s="2" t="inlineStr">
@@ -21399,7 +21399,7 @@
       </c>
       <c r="N243" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O243" s="2" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="N244" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O244" s="2" t="inlineStr">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="N245" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O245" s="2" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="N246" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O246" s="2" t="inlineStr">
@@ -22343,7 +22343,7 @@
       </c>
       <c r="N254" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes</t>
         </is>
       </c>
       <c r="O254" s="2" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="N255" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : comparée dans data/evolutions.json</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : comparée dans data/evolutions.json</t>
         </is>
       </c>
       <c r="O255" s="2" t="inlineStr">
@@ -22515,7 +22515,7 @@
       </c>
       <c r="N256" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
         </is>
       </c>
       <c r="O256" s="2" t="inlineStr">
@@ -22603,7 +22603,7 @@
       </c>
       <c r="N257" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O257" s="2" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="N258" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O258" s="2" t="inlineStr">
@@ -22771,7 +22771,7 @@
       </c>
       <c r="N259" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O259" s="2" t="inlineStr">
@@ -22855,7 +22855,7 @@
       </c>
       <c r="N260" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
         </is>
       </c>
       <c r="O260" s="2" t="inlineStr">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="N261" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O261" s="2" t="inlineStr">
@@ -23023,7 +23023,7 @@
       </c>
       <c r="N262" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : fait daté ou tendance déclarée, pas une évolution calculée</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : fait daté ou tendance déclarée, pas une évolution calculée</t>
         </is>
       </c>
       <c r="O262" s="2" t="inlineStr">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="N263" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, règles d'affichage (réponse changée à l'écran)) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
         </is>
       </c>
       <c r="O263" s="2" t="inlineStr">
@@ -23195,7 +23195,7 @@
       </c>
       <c r="N264" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O264" s="2" t="inlineStr">
@@ -23279,7 +23279,7 @@
       </c>
       <c r="N265" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O265" s="2" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="N266" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O266" s="2" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="N267" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
         </is>
       </c>
       <c r="O267" s="2" t="inlineStr">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="N268" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
         </is>
       </c>
       <c r="O268" s="2" t="inlineStr">
@@ -23615,7 +23615,7 @@
       </c>
       <c r="N269" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O269" s="2" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="N270" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O270" s="2" t="inlineStr">
@@ -23783,7 +23783,7 @@
       </c>
       <c r="N271" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O271" s="2" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="N272" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O272" s="2" t="inlineStr">
@@ -24039,7 +24039,7 @@
       </c>
       <c r="N274" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O274" s="2" t="inlineStr">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="N275" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O275" s="2" t="inlineStr">
@@ -24203,7 +24203,7 @@
       </c>
       <c r="N276" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O276" s="2" t="inlineStr">
@@ -24295,7 +24295,7 @@
       </c>
       <c r="N277" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : taille absente des comptes de test (2 à 5 personnes)</t>
         </is>
       </c>
       <c r="O277" s="2" t="inlineStr">
@@ -24459,7 +24459,7 @@
       </c>
       <c r="N279" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : taille absente des comptes de test (2 à 5 personnes)</t>
         </is>
       </c>
       <c r="O279" s="2" t="inlineStr">
@@ -24539,7 +24539,7 @@
       </c>
       <c r="N280" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O280" s="2" t="inlineStr">
@@ -24619,7 +24619,7 @@
       </c>
       <c r="N281" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O281" s="2" t="inlineStr">
@@ -24699,7 +24699,7 @@
       </c>
       <c r="N282" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O282" s="2" t="inlineStr">
@@ -24779,7 +24779,7 @@
       </c>
       <c r="N283" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O283" s="2" t="inlineStr">
@@ -24859,7 +24859,7 @@
       </c>
       <c r="N284" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O284" s="2" t="inlineStr">
@@ -24943,7 +24943,7 @@
       </c>
       <c r="N285" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O285" s="2" t="inlineStr">
@@ -25027,7 +25027,7 @@
       </c>
       <c r="N286" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O286" s="2" t="inlineStr">
@@ -25107,7 +25107,7 @@
       </c>
       <c r="N287" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O287" s="2" t="inlineStr">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="N288" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O288" s="2" t="inlineStr">
@@ -25267,7 +25267,7 @@
       </c>
       <c r="N289" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O289" s="2" t="inlineStr">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="N297" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O297" s="2" t="inlineStr">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="N298" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (partages, boutons de réponse) | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, partages, boutons de réponse) | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
         </is>
       </c>
       <c r="O298" s="2" t="inlineStr">
@@ -26083,7 +26083,7 @@
       </c>
       <c r="N299" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O299" s="2" t="inlineStr">
@@ -26167,7 +26167,7 @@
       </c>
       <c r="N300" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O300" s="2" t="inlineStr">
@@ -26251,7 +26251,7 @@
       </c>
       <c r="N301" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O301" s="2" t="inlineStr">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O302" s="2" t="inlineStr">
@@ -26419,7 +26419,7 @@
       </c>
       <c r="N303" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O303" s="2" t="inlineStr">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="N306" s="2" t="inlineStr">
         <is>
-          <t>corrigée (règle) : Doublon : la même question (« La personne la plus chargée, est-ce vous ? ») est posée au cadrage (D27) puis ici. RH-08.02 et RH-08.04 suivaient le cadrage seul : avec « Vous » au cadrage et « Une personne à l'administratif » ici, les questions sur cette personne disparaissaient. Correction : D27 devient la réponse à RH-08.01 (comme D03 → ACQ-03.01), le cadrage n'est plus posé. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>corrigée (règle) : Doublon : la même question (« La personne la plus chargée, est-ce vous ? ») est posée au cadrage (D27) puis ici. RH-08.02 et RH-08.04 suivaient le cadrage seul : avec « Vous » au cadrage et « Une personne à l'administratif » ici, les questions sur cette personne disparaissaient. Correction : D27 devient la réponse à RH-08.01 (comme D03 → ACQ-03.01), le cadrage n'est plus posé. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O306" s="2" t="inlineStr">
@@ -26759,7 +26759,7 @@
       </c>
       <c r="N307" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O307" s="2" t="inlineStr">
@@ -26839,7 +26839,7 @@
       </c>
       <c r="N308" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O308" s="2" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="N309" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O309" s="2" t="inlineStr">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="N310" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O310" s="2" t="inlineStr">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="N311" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O311" s="2" t="inlineStr">
@@ -27155,7 +27155,7 @@
       </c>
       <c r="N312" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O312" s="2" t="inlineStr">
@@ -27235,7 +27235,7 @@
       </c>
       <c r="N313" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : tranches qui se chevauchent → faux positif : unités différentes (jours, semaines) | contrôle automatique : tranches qui se chevauchent → faux positif : unités différentes (jours, semaines)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : tranches qui se chevauchent → faux positif : unités différentes (jours, semaines) | contrôle automatique : tranches qui se chevauchent → faux positif : unités différentes (jours, semaines)</t>
         </is>
       </c>
       <c r="O313" s="2" t="inlineStr">
@@ -27319,7 +27319,7 @@
       </c>
       <c r="N314" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O314" s="2" t="inlineStr">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="N328" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O328" s="2" t="inlineStr">
@@ -28799,7 +28799,7 @@
       </c>
       <c r="N332" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O332" s="2" t="inlineStr">
@@ -28875,7 +28875,7 @@
       </c>
       <c r="N333" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O333" s="2" t="inlineStr">
@@ -28967,7 +28967,7 @@
       </c>
       <c r="N334" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (partages, boutons de réponse) | A-02 corrigée le 29 octobre (Navigateur : P-07a à P-07d, P-13 à P-19b conformes (dont la reprise non enregistrée, la question complétée puis enregistrée, la modification depuis l'autre agent et après actualisation))</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), partages, boutons de réponse) | A-02 corrigée le 29 octobre (Navigateur : P-07a à P-07d, P-13 à P-19b conformes (dont la reprise non enregistrée, la question complétée puis enregistrée, la modification depuis l'autre agent et après actualisation))</t>
         </is>
       </c>
       <c r="O334" s="2" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="N335" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O335" s="2" t="inlineStr">
@@ -29131,7 +29131,7 @@
       </c>
       <c r="N336" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O336" s="2" t="inlineStr">
@@ -29455,7 +29455,7 @@
       </c>
       <c r="N340" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O340" s="2" t="inlineStr">
@@ -29551,7 +29551,7 @@
       </c>
       <c r="N341" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O341" s="2" t="inlineStr">
@@ -29631,7 +29631,7 @@
       </c>
       <c r="N342" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O342" s="2" t="inlineStr">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="N343" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O343" s="2" t="inlineStr">
@@ -29795,7 +29795,7 @@
       </c>
       <c r="N344" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O344" s="2" t="inlineStr">
@@ -29875,7 +29875,7 @@
       </c>
       <c r="N345" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O345" s="2" t="inlineStr">
@@ -29967,7 +29967,7 @@
       </c>
       <c r="N346" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O346" s="2" t="inlineStr">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="N347" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O347" s="2" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="N348" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O348" s="2" t="inlineStr">
@@ -30223,7 +30223,7 @@
       </c>
       <c r="N349" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O349" s="2" t="inlineStr">
@@ -30311,7 +30311,7 @@
       </c>
       <c r="N350" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage)</t>
         </is>
       </c>
       <c r="O350" s="2" t="inlineStr">
@@ -30391,7 +30391,7 @@
       </c>
       <c r="N351" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O351" s="2" t="inlineStr">
@@ -30559,7 +30559,7 @@
       </c>
       <c r="N353" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O353" s="2" t="inlineStr">
@@ -30651,7 +30651,7 @@
       </c>
       <c r="N354" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O354" s="2" t="inlineStr">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="N355" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O355" s="2" t="inlineStr">
@@ -30823,7 +30823,7 @@
       </c>
       <c r="N356" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O356" s="2" t="inlineStr">
@@ -30903,7 +30903,7 @@
       </c>
       <c r="N357" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O357" s="2" t="inlineStr">
@@ -30983,7 +30983,7 @@
       </c>
       <c r="N358" s="2" t="inlineStr">
         <is>
-          <t>corrigée (règle) : Doublon : la même question est posée au cadrage (D13 « Avez-vous recruté sur la période, ou prévoyez-vous de recruter ? ») puis ici, avec des choix différents. Les questions de recrutement (RH-28 à RH-33) suivaient le cadrage seul : deux réponses contradictoires étaient possibles. Correction : D13 devient la réponse à RH-28.01, le cadrage n'est plus posé ; « Les deux » compte comme « recruté » et « prévu ». | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : recrutement : condition à vérifier → conforme : posée si recrutement fait ou prévu (D13)</t>
+          <t>corrigée (règle) : Doublon : la même question est posée au cadrage (D13 « Avez-vous recruté sur la période, ou prévoyez-vous de recruter ? ») puis ici, avec des choix différents. Les questions de recrutement (RH-28 à RH-33) suivaient le cadrage seul : deux réponses contradictoires étaient possibles. Correction : D13 devient la réponse à RH-28.01, le cadrage n'est plus posé ; « Les deux » compte comme « recruté » et « prévu ». | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse) | contrôle automatique : recrutement : condition à vérifier → conforme : posée si recrutement fait ou prévu (D13)</t>
         </is>
       </c>
       <c r="O358" s="2" t="inlineStr">
@@ -31071,7 +31071,7 @@
       </c>
       <c r="N359" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O359" s="2" t="inlineStr">
@@ -31151,7 +31151,7 @@
       </c>
       <c r="N360" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation (tranches : A-11) | contrôle automatique : zéro impossible à choisir → faux positif (tranches non contiguës : A-11)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation (tranches : A-11) | contrôle automatique : zéro impossible à choisir → faux positif (tranches non contiguës : A-11)</t>
         </is>
       </c>
       <c r="O360" s="2" t="inlineStr">
@@ -31239,7 +31239,7 @@
       </c>
       <c r="N361" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles) | contrôle automatique : recrutement : condition à vérifier → conforme : posée si recrutement fait ou prévu (D13)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles) | contrôle automatique : recrutement : condition à vérifier → conforme : posée si recrutement fait ou prévu (D13)</t>
         </is>
       </c>
       <c r="O361" s="2" t="inlineStr">
@@ -31319,7 +31319,7 @@
       </c>
       <c r="N362" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles) | contrôle automatique : recrutement : condition à vérifier → conforme : posée si recrutement fait ou prévu (D13) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles) | contrôle automatique : recrutement : condition à vérifier → conforme : posée si recrutement fait ou prévu (D13) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O362" s="2" t="inlineStr">
@@ -31399,7 +31399,7 @@
       </c>
       <c r="N363" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : taille absente des comptes de test (2 à 5 personnes)</t>
         </is>
       </c>
       <c r="O363" s="2" t="inlineStr">
@@ -31475,7 +31475,7 @@
       </c>
       <c r="N364" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : recrutement : condition à vérifier → conforme : posée si recrutement fait ou prévu (D13)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : recrutement : condition à vérifier → conforme : posée si recrutement fait ou prévu (D13)</t>
         </is>
       </c>
       <c r="O364" s="2" t="inlineStr">
@@ -31555,7 +31555,7 @@
       </c>
       <c r="N365" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-07</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-07</t>
         </is>
       </c>
       <c r="O365" s="2" t="inlineStr">
@@ -31643,7 +31643,7 @@
       </c>
       <c r="N366" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul | contrôle automatique : financement : condition à vérifier → faux positif (« prêt » au sens de préparé)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul | contrôle automatique : financement : condition à vérifier → faux positif (« prêt » au sens de préparé)</t>
         </is>
       </c>
       <c r="O366" s="2" t="inlineStr">
@@ -31723,7 +31723,7 @@
       </c>
       <c r="N367" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul</t>
         </is>
       </c>
       <c r="O367" s="2" t="inlineStr">
@@ -31803,7 +31803,7 @@
       </c>
       <c r="N368" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul</t>
         </is>
       </c>
       <c r="O368" s="2" t="inlineStr">
@@ -31883,7 +31883,7 @@
       </c>
       <c r="N369" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul</t>
         </is>
       </c>
       <c r="O369" s="2" t="inlineStr">
@@ -31963,7 +31963,7 @@
       </c>
       <c r="N370" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O370" s="2" t="inlineStr">
@@ -32047,7 +32047,7 @@
       </c>
       <c r="N371" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O371" s="2" t="inlineStr">
@@ -32127,7 +32127,7 @@
       </c>
       <c r="N372" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O372" s="2" t="inlineStr">
@@ -32207,7 +32207,7 @@
       </c>
       <c r="N373" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O373" s="2" t="inlineStr">
@@ -32287,7 +32287,7 @@
       </c>
       <c r="N374" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O374" s="2" t="inlineStr">
@@ -32363,7 +32363,7 @@
       </c>
       <c r="N375" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O375" s="2" t="inlineStr">
@@ -32447,7 +32447,7 @@
       </c>
       <c r="N376" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O376" s="2" t="inlineStr">
@@ -32531,7 +32531,7 @@
       </c>
       <c r="N377" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O377" s="2" t="inlineStr">
@@ -32611,7 +32611,7 @@
       </c>
       <c r="N378" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O378" s="2" t="inlineStr">
@@ -32691,7 +32691,7 @@
       </c>
       <c r="N379" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O379" s="2" t="inlineStr">
@@ -32771,7 +32771,7 @@
       </c>
       <c r="N380" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O380" s="2" t="inlineStr">
@@ -32863,7 +32863,7 @@
       </c>
       <c r="N381" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O381" s="2" t="inlineStr">
@@ -32955,7 +32955,7 @@
       </c>
       <c r="N382" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O382" s="2" t="inlineStr">
@@ -33043,7 +33043,7 @@
       </c>
       <c r="N383" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O383" s="2" t="inlineStr">
@@ -33127,7 +33127,7 @@
       </c>
       <c r="N384" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O384" s="2" t="inlineStr">
@@ -33215,7 +33215,7 @@
       </c>
       <c r="N385" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O385" s="2" t="inlineStr">
@@ -33295,7 +33295,7 @@
       </c>
       <c r="N386" s="2" t="inlineStr">
         <is>
-          <t>reformulée : Choix incomplet : une entreprise sans changement d'organisation récent ne peut pas répondre. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>reformulée : Choix incomplet : une entreprise sans changement d'organisation récent ne peut pas répondre. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O386" s="2" t="inlineStr">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="N388" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul</t>
         </is>
       </c>
       <c r="O388" s="2" t="inlineStr">
@@ -33547,7 +33547,7 @@
       </c>
       <c r="N389" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O389" s="2" t="inlineStr">
@@ -33627,7 +33627,7 @@
       </c>
       <c r="N390" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O390" s="2" t="inlineStr">
@@ -33707,7 +33707,7 @@
       </c>
       <c r="N391" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O391" s="2" t="inlineStr">
@@ -33787,7 +33787,7 @@
       </c>
       <c r="N392" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles) | contrôle automatique : question double pour un seul champ → conforme : texte libre lu par l'IA</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles) | contrôle automatique : question double pour un seul champ → conforme : texte libre lu par l'IA</t>
         </is>
       </c>
       <c r="O392" s="2" t="inlineStr">
@@ -33867,7 +33867,7 @@
       </c>
       <c r="N393" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O393" s="2" t="inlineStr">
@@ -33955,7 +33955,7 @@
       </c>
       <c r="N394" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O394" s="2" t="inlineStr">
@@ -34031,7 +34031,7 @@
       </c>
       <c r="N395" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O395" s="2" t="inlineStr">
@@ -34111,7 +34111,7 @@
       </c>
       <c r="N396" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O396" s="2" t="inlineStr">
@@ -34195,7 +34195,7 @@
       </c>
       <c r="N397" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, règles d'affichage (réponse changée à l'écran), branches des règles) | contrôle automatique : équipe : posée au dirigeant seul → conforme : se répond en estimation, ou écrite pour le dirigeant seul</t>
         </is>
       </c>
       <c r="O397" s="2" t="inlineStr">
@@ -34271,7 +34271,7 @@
       </c>
       <c r="N398" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O398" s="2" t="inlineStr">
@@ -34351,7 +34351,7 @@
       </c>
       <c r="N399" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O399" s="2" t="inlineStr">
@@ -34431,7 +34431,7 @@
       </c>
       <c r="N400" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O400" s="2" t="inlineStr">
@@ -34511,7 +34511,7 @@
       </c>
       <c r="N401" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O401" s="2" t="inlineStr">
@@ -34603,7 +34603,7 @@
       </c>
       <c r="N402" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O402" s="2" t="inlineStr">
@@ -34687,7 +34687,7 @@
       </c>
       <c r="N403" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O403" s="2" t="inlineStr">
@@ -35123,7 +35123,7 @@
       </c>
       <c r="N408" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O408" s="2" t="inlineStr">
@@ -35211,7 +35211,7 @@
       </c>
       <c r="N409" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O409" s="2" t="inlineStr">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="N416" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O416" s="2" t="inlineStr">
@@ -35907,7 +35907,7 @@
       </c>
       <c r="N417" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O417" s="2" t="inlineStr">
@@ -35991,7 +35991,7 @@
       </c>
       <c r="N418" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O418" s="2" t="inlineStr">
@@ -36075,7 +36075,7 @@
       </c>
       <c r="N419" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O419" s="2" t="inlineStr">
@@ -36155,7 +36155,7 @@
       </c>
       <c r="N420" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O420" s="2" t="inlineStr">
@@ -36239,7 +36239,7 @@
       </c>
       <c r="N421" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O421" s="2" t="inlineStr">
@@ -36323,7 +36323,7 @@
       </c>
       <c r="N422" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles)</t>
         </is>
       </c>
       <c r="O422" s="2" t="inlineStr">
@@ -36407,7 +36407,7 @@
       </c>
       <c r="N423" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O423" s="2" t="inlineStr">
@@ -36591,7 +36591,7 @@
       </c>
       <c r="N425" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : posée seulement si « Site internet » n'est pas coché</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : posée seulement si « Site internet » n'est pas coché</t>
         </is>
       </c>
       <c r="O425" s="2" t="inlineStr">
@@ -36683,7 +36683,7 @@
       </c>
       <c r="N426" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (partages, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, partages, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
         </is>
       </c>
       <c r="O426" s="2" t="inlineStr">
@@ -36775,7 +36775,7 @@
       </c>
       <c r="N427" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, règles d'affichage (réponse changée à l'écran), boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O427" s="2" t="inlineStr">
@@ -36859,7 +36859,7 @@
       </c>
       <c r="N428" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O428" s="2" t="inlineStr">
@@ -36943,7 +36943,7 @@
       </c>
       <c r="N429" s="2" t="inlineStr">
         <is>
-          <t>reformulée : Période absente pour une répartition des visites. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>reformulée : Période absente pour une répartition des visites. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O429" s="2" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="N430" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O430" s="2" t="inlineStr">
@@ -37119,7 +37119,7 @@
       </c>
       <c r="N431" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : comparée dans data/evolutions.json</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : comparaison avec le passé : évolution à vérifier → conforme : comparée dans data/evolutions.json</t>
         </is>
       </c>
       <c r="O431" s="2" t="inlineStr">
@@ -37203,7 +37203,7 @@
       </c>
       <c r="N432" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O432" s="2" t="inlineStr">
@@ -37291,7 +37291,7 @@
       </c>
       <c r="N433" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O433" s="2" t="inlineStr">
@@ -37375,7 +37375,7 @@
       </c>
       <c r="N434" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O434" s="2" t="inlineStr">
@@ -37459,7 +37459,7 @@
       </c>
       <c r="N435" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O435" s="2" t="inlineStr">
@@ -37543,7 +37543,7 @@
       </c>
       <c r="N436" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O436" s="2" t="inlineStr">
@@ -37631,7 +37631,7 @@
       </c>
       <c r="N437" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O437" s="2" t="inlineStr">
@@ -37715,7 +37715,7 @@
       </c>
       <c r="N438" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O438" s="2" t="inlineStr">
@@ -37799,7 +37799,7 @@
       </c>
       <c r="N439" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O439" s="2" t="inlineStr">
@@ -37883,7 +37883,7 @@
       </c>
       <c r="N440" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O440" s="2" t="inlineStr">
@@ -37967,7 +37967,7 @@
       </c>
       <c r="N441" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : condition non remplie par les réponses des contrôles</t>
         </is>
       </c>
       <c r="O441" s="2" t="inlineStr">
@@ -38051,7 +38051,7 @@
       </c>
       <c r="N442" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, règles d'affichage (réponse changée à l'écran), branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O442" s="2" t="inlineStr">
@@ -38299,7 +38299,7 @@
       </c>
       <c r="N445" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O445" s="2" t="inlineStr">
@@ -38387,7 +38387,7 @@
       </c>
       <c r="N446" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O446" s="2" t="inlineStr">
@@ -38471,7 +38471,7 @@
       </c>
       <c r="N447" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : comparaison avec le passé : évolution à vérifier → évolution par réseau non calculée, décision en attente (A-15)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : comparaison avec le passé : évolution à vérifier → évolution par réseau non calculée, décision en attente (A-15)</t>
         </is>
       </c>
       <c r="O447" s="2" t="inlineStr">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="N448" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O448" s="2" t="inlineStr">
@@ -38647,7 +38647,7 @@
       </c>
       <c r="N449" s="2" t="inlineStr">
         <is>
-          <t>reformulée : Période absente. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>reformulée : Période absente. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O449" s="2" t="inlineStr">
@@ -38731,7 +38731,7 @@
       </c>
       <c r="N450" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O450" s="2" t="inlineStr">
@@ -38811,7 +38811,7 @@
       </c>
       <c r="N451" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O451" s="2" t="inlineStr">
@@ -38895,7 +38895,7 @@
       </c>
       <c r="N452" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O452" s="2" t="inlineStr">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="N453" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O453" s="2" t="inlineStr">
@@ -39071,7 +39071,7 @@
       </c>
       <c r="N454" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O454" s="2" t="inlineStr">
@@ -39155,7 +39155,7 @@
       </c>
       <c r="N455" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O455" s="2" t="inlineStr">
@@ -39239,7 +39239,7 @@
       </c>
       <c r="N456" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O456" s="2" t="inlineStr">
@@ -39323,7 +39323,7 @@
       </c>
       <c r="N457" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, règles d'affichage (réponse changée à l'écran), branches des règles, boutons de réponse) | contrôle automatique : texte très proche d'une autre question → conforme : questions différentes</t>
         </is>
       </c>
       <c r="O457" s="2" t="inlineStr">
@@ -39407,7 +39407,7 @@
       </c>
       <c r="N458" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O458" s="2" t="inlineStr">
@@ -39499,7 +39499,7 @@
       </c>
       <c r="N459" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O459" s="2" t="inlineStr">
@@ -39583,7 +39583,7 @@
       </c>
       <c r="N460" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O460" s="2" t="inlineStr">
@@ -39667,7 +39667,7 @@
       </c>
       <c r="N461" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O461" s="2" t="inlineStr">
@@ -39751,7 +39751,7 @@
       </c>
       <c r="N462" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O462" s="2" t="inlineStr">
@@ -39831,7 +39831,7 @@
       </c>
       <c r="N463" s="2" t="inlineStr">
         <is>
-          <t>reformulée : Une seule répartition pour deux populations différentes (« les clients et les demandes ») et sans période. Mesure précisée sur les demandes, comme la ligne « Réseaux sociaux » de la répartition des demandes par canal (ACQ-03.02) : à valider. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>reformulée : Une seule répartition pour deux populations différentes (« les clients et les demandes ») et sans période. Mesure précisée sur les demandes, comme la ligne « Réseaux sociaux » de la répartition des demandes par canal (ACQ-03.02) : à valider. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage)</t>
         </is>
       </c>
       <c r="O463" s="2" t="inlineStr">
@@ -39923,7 +39923,7 @@
       </c>
       <c r="N464" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O464" s="2" t="inlineStr">
@@ -40007,7 +40007,7 @@
       </c>
       <c r="N465" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, règles d'affichage (réponse changée à l'écran), branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O465" s="2" t="inlineStr">
@@ -40091,7 +40091,7 @@
       </c>
       <c r="N466" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O466" s="2" t="inlineStr">
@@ -40271,7 +40271,7 @@
       </c>
       <c r="N468" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O468" s="2" t="inlineStr">
@@ -40359,7 +40359,7 @@
       </c>
       <c r="N469" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O469" s="2" t="inlineStr">
@@ -40443,7 +40443,7 @@
       </c>
       <c r="N470" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O470" s="2" t="inlineStr">
@@ -40615,7 +40615,7 @@
       </c>
       <c r="N472" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-10</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-10</t>
         </is>
       </c>
       <c r="O472" s="2" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="N473" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-10</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | contrôle automatique : équipe : posée au dirigeant seul → anomalie A-10</t>
         </is>
       </c>
       <c r="O473" s="2" t="inlineStr">
@@ -40799,7 +40799,7 @@
       </c>
       <c r="N474" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O474" s="2" t="inlineStr">
@@ -40883,7 +40883,7 @@
       </c>
       <c r="N475" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O475" s="2" t="inlineStr">
@@ -41235,7 +41235,7 @@
       </c>
       <c r="N479" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O479" s="2" t="inlineStr">
@@ -41319,7 +41319,7 @@
       </c>
       <c r="N480" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O480" s="2" t="inlineStr">
@@ -41411,7 +41411,7 @@
       </c>
       <c r="N481" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O481" s="2" t="inlineStr">
@@ -41495,7 +41495,7 @@
       </c>
       <c r="N482" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O482" s="2" t="inlineStr">
@@ -41579,7 +41579,7 @@
       </c>
       <c r="N483" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O483" s="2" t="inlineStr">
@@ -41667,7 +41667,7 @@
       </c>
       <c r="N484" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O484" s="2" t="inlineStr">
@@ -41759,7 +41759,7 @@
       </c>
       <c r="N485" s="2" t="inlineStr">
         <is>
-          <t>reformulée : « Ces 6 publications » renvoie à COM-39.01, qui n'est pas posée quand les statistiques sont connectées (D26) : la question reste alors sans référence. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>reformulée : « Ces 6 publications » renvoie à COM-39.01, qui n'est pas posée quand les statistiques sont connectées (D26) : la question reste alors sans référence. | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O485" s="2" t="inlineStr">
@@ -41851,7 +41851,7 @@
       </c>
       <c r="N486" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O486" s="2" t="inlineStr">
@@ -42019,7 +42019,7 @@
       </c>
       <c r="N488" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O488" s="2" t="inlineStr">
@@ -42107,7 +42107,7 @@
       </c>
       <c r="N489" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse) | A-02 corrigée le 29 octobre (Navigateur : P-07a à P-07d, P-13 à P-19b conformes (dont la reprise non enregistrée, la question complétée puis enregistrée, la modification depuis l'autre agent et après actualisation))</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse) | A-02 corrigée le 29 octobre (Navigateur : P-07a à P-07d, P-13 à P-19b conformes (dont la reprise non enregistrée, la question complétée puis enregistrée, la modification depuis l'autre agent et après actualisation))</t>
         </is>
       </c>
       <c r="O489" s="2" t="inlineStr">
@@ -42191,7 +42191,7 @@
       </c>
       <c r="N490" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O490" s="2" t="inlineStr">
@@ -42283,7 +42283,7 @@
       </c>
       <c r="N491" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → anomalie A-09 | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → anomalie A-09 | A-01 corrigée le 29 octobre (Navigateur : scripts/verification/partages)</t>
         </is>
       </c>
       <c r="O491" s="2" t="inlineStr">
@@ -42463,7 +42463,7 @@
       </c>
       <c r="N493" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O493" s="2" t="inlineStr">
@@ -42547,7 +42547,7 @@
       </c>
       <c r="N494" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O494" s="2" t="inlineStr">
@@ -42639,7 +42639,7 @@
       </c>
       <c r="N495" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse)</t>
         </is>
       </c>
       <c r="O495" s="2" t="inlineStr">
@@ -42719,7 +42719,7 @@
       </c>
       <c r="N496" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O496" s="2" t="inlineStr">
@@ -42807,7 +42807,7 @@
       </c>
       <c r="N497" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O497" s="2" t="inlineStr">
@@ -42891,7 +42891,7 @@
       </c>
       <c r="N498" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O498" s="2" t="inlineStr">
@@ -42975,7 +42975,7 @@
       </c>
       <c r="N499" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (branches des règles, boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, branches des règles, boutons de réponse)</t>
         </is>
       </c>
       <c r="O499" s="2" t="inlineStr">
@@ -43151,7 +43151,7 @@
       </c>
       <c r="N501" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier)</t>
         </is>
       </c>
       <c r="O501" s="2" t="inlineStr">
@@ -44639,7 +44639,7 @@
       </c>
       <c r="N518" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O518" s="2" t="inlineStr">
@@ -44731,7 +44731,7 @@
       </c>
       <c r="N519" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : unité différente du texte → faux positif : une part du chiffre d'affaires se répond en %</t>
         </is>
       </c>
       <c r="O519" s="2" t="inlineStr">
@@ -44823,7 +44823,7 @@
       </c>
       <c r="N520" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : profil absent des comptes de test (électricien, profil chantier) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O520" s="2" t="inlineStr">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="N525" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O525" s="2" t="inlineStr">
@@ -45343,7 +45343,7 @@
       </c>
       <c r="N526" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O526" s="2" t="inlineStr">
@@ -45427,7 +45427,7 @@
       </c>
       <c r="N527" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : zéro impossible à saisir → faux positif : position dans Google et effectif « vous compris » valent au moins 1</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : zéro impossible à saisir → faux positif : position dans Google et effectif « vous compris » valent au moins 1</t>
         </is>
       </c>
       <c r="O527" s="2" t="inlineStr">
@@ -45515,7 +45515,7 @@
       </c>
       <c r="N528" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : zéro impossible à saisir → faux positif : position dans Google et effectif « vous compris » valent au moins 1</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente | contrôle automatique : zéro impossible à saisir → faux positif : position dans Google et effectif « vous compris » valent au moins 1</t>
         </is>
       </c>
       <c r="O528" s="2" t="inlineStr">
@@ -45607,7 +45607,7 @@
       </c>
       <c r="N529" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O529" s="2" t="inlineStr">
@@ -45695,7 +45695,7 @@
       </c>
       <c r="N530" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O530" s="2" t="inlineStr">
@@ -45779,7 +45779,7 @@
       </c>
       <c r="N531" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O531" s="2" t="inlineStr">
@@ -45863,7 +45863,7 @@
       </c>
       <c r="N532" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O532" s="2" t="inlineStr">
@@ -45947,7 +45947,7 @@
       </c>
       <c r="N533" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O533" s="2" t="inlineStr">
@@ -46035,7 +46035,7 @@
       </c>
       <c r="N534" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → question qui ouvre le bloc ; se déduit de D04 = non (A-20)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran), boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → question qui ouvre le bloc ; se déduit de D04 = non (A-20)</t>
         </is>
       </c>
       <c r="O534" s="2" t="inlineStr">
@@ -46127,7 +46127,7 @@
       </c>
       <c r="N535" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O535" s="2" t="inlineStr">
@@ -46215,7 +46215,7 @@
       </c>
       <c r="N536" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O536" s="2" t="inlineStr">
@@ -46303,7 +46303,7 @@
       </c>
       <c r="N537" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O537" s="2" t="inlineStr">
@@ -46387,7 +46387,7 @@
       </c>
       <c r="N538" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O538" s="2" t="inlineStr">
@@ -46471,7 +46471,7 @@
       </c>
       <c r="N539" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O539" s="2" t="inlineStr">
@@ -46555,7 +46555,7 @@
       </c>
       <c r="N540" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse)</t>
         </is>
       </c>
       <c r="O540" s="2" t="inlineStr">
@@ -46639,7 +46639,7 @@
       </c>
       <c r="N541" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | affichée et manipulée dans l'application (règles d'affichage, boutons de réponse) | contrôle automatique : canal ou outil : condition à vérifier → conforme : condition sur le canal ou l'outil présente</t>
         </is>
       </c>
       <c r="O541" s="2" t="inlineStr">
@@ -46723,7 +46723,7 @@
       </c>
       <c r="N542" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O542" s="2" t="inlineStr">
@@ -46811,7 +46811,7 @@
       </c>
       <c r="N543" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O543" s="2" t="inlineStr">
@@ -46899,7 +46899,7 @@
       </c>
       <c r="N544" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O544" s="2" t="inlineStr">
@@ -46983,7 +46983,7 @@
       </c>
       <c r="N545" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O545" s="2" t="inlineStr">
@@ -47067,7 +47067,7 @@
       </c>
       <c r="N546" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O546" s="2" t="inlineStr">
@@ -47151,7 +47151,7 @@
       </c>
       <c r="N547" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O547" s="2" t="inlineStr">
@@ -47239,7 +47239,7 @@
       </c>
       <c r="N548" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien) | contrôle automatique : montant sans HT ni TTC → anomalie A-05 | contrôle automatique : montant sans HT ni TTC → anomalie A-05</t>
         </is>
       </c>
       <c r="O548" s="2" t="inlineStr">
@@ -47323,7 +47323,7 @@
       </c>
       <c r="N549" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O549" s="2" t="inlineStr">
@@ -47407,7 +47407,7 @@
       </c>
       <c r="N550" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
         </is>
       </c>
       <c r="O550" s="2" t="inlineStr">
@@ -47491,7 +47491,7 @@
       </c>
       <c r="N551" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O551" s="2" t="inlineStr">
@@ -47579,7 +47579,7 @@
       </c>
       <c r="N552" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : financement : condition à vérifier → conforme : module métier validé (véhicules)</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien) | contrôle automatique : financement : condition à vérifier → conforme : module métier validé (véhicules)</t>
         </is>
       </c>
       <c r="O552" s="2" t="inlineStr">
@@ -47663,7 +47663,7 @@
       </c>
       <c r="N553" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien) | contrôle automatique : stock : condition à vérifier → conforme : posée si stock (D07) ou module métier du stock de biens</t>
         </is>
       </c>
       <c r="O553" s="2" t="inlineStr">
@@ -47747,7 +47747,7 @@
       </c>
       <c r="N554" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O554" s="2" t="inlineStr">
@@ -47831,7 +47831,7 @@
       </c>
       <c r="N555" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O555" s="2" t="inlineStr">
@@ -47915,7 +47915,7 @@
       </c>
       <c r="N556" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O556" s="2" t="inlineStr">
@@ -47999,7 +47999,7 @@
       </c>
       <c r="N557" s="2" t="inlineStr">
         <is>
-          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur</t>
+          <t>relue (texte, aide, choix, unité, période) | assemblée par le vrai code et contrôlée dans les 7 704 questionnaires du balayage | non manipulée dans le navigateur : module métier (comptes de test : électricien)</t>
         </is>
       </c>
       <c r="O557" s="2" t="inlineStr">
@@ -49007,7 +49007,7 @@
       </c>
       <c r="N570" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O570" s="2" t="inlineStr">
@@ -49091,7 +49091,7 @@
       </c>
       <c r="N571" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O571" s="2" t="inlineStr">
@@ -49171,7 +49171,7 @@
       </c>
       <c r="N572" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O572" s="2" t="inlineStr">
@@ -49251,7 +49251,7 @@
       </c>
       <c r="N573" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O573" s="2" t="inlineStr">
@@ -49335,7 +49335,7 @@
       </c>
       <c r="N574" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O574" s="2" t="inlineStr">
@@ -49415,7 +49415,7 @@
       </c>
       <c r="N575" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O575" s="2" t="inlineStr">
@@ -49495,7 +49495,7 @@
       </c>
       <c r="N576" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O576" s="2" t="inlineStr">
@@ -49575,7 +49575,7 @@
       </c>
       <c r="N577" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O577" s="2" t="inlineStr">
@@ -49659,7 +49659,7 @@
       </c>
       <c r="N578" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O578" s="2" t="inlineStr">
@@ -49815,7 +49815,7 @@
       </c>
       <c r="N580" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O580" s="2" t="inlineStr">
@@ -49975,7 +49975,7 @@
       </c>
       <c r="N582" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O582" s="2" t="inlineStr">
@@ -50055,7 +50055,7 @@
       </c>
       <c r="N583" s="2" t="inlineStr">
         <is>
-          <t>relue (question de cadrage)</t>
+          <t>relue (question de cadrage) | affichée et manipulée dans l'application (règles d'affichage (réponse changée à l'écran))</t>
         </is>
       </c>
       <c r="O583" s="2" t="inlineStr">
@@ -51000,7 +51000,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>à construire</t>
+          <t>faite</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -51020,12 +51020,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Brancher bilanNonSuivi dans le constat transmis à l'IA du compte rendu ; le texte du conseil reste à écrire.</t>
+          <t>Branché le 29 octobre : bilanNonSuivi alimente le dossier du rapport (suiviDonnees : nombre de données non suivies, données essentielles, déclenché au-delà d'un quart) ; les consignes demandent alors à l'IA un conseil général de pilotage qui complète les autres. Le texte du conseil est rédigé par l'IA ; aucun appel réel n'a encore été fait.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Recherche dans le code : aucun appel hors des tests.</t>
+          <t>src/lib/rapport/rapport-compte.ts (preparerDuCompte) et src/lib/rapport/prompt.ts ; tests/rapport.test.mts (dossier). Appel réel non essayé.</t>
         </is>
       </c>
     </row>
@@ -51501,7 +51501,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>360</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10">
@@ -51642,7 +51642,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>A-01, A-02, A-03, A-04</t>
+          <t>A-01, A-02, A-03, A-04, A-16</t>
         </is>
       </c>
     </row>
@@ -51678,7 +51678,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>A-16, A-21</t>
+          <t>A-21</t>
         </is>
       </c>
     </row>
